--- a/ky/downloads/data-excel/4.3.1.1.xlsx
+++ b/ky/downloads/data-excel/4.3.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B81AA3-514C-4004-920A-7825422E0C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,12 +48,6 @@
     <t>Процент охвата молодежи высшим профессиональным образованием (от населения в возрасте 17-24 лет)</t>
   </si>
   <si>
-    <t>4.3.1.1 Образованность молодежи по полу</t>
-  </si>
-  <si>
-    <t>4.3.1.1 Жынынсы боюнча жаштардын билимдүүлүгү</t>
-  </si>
-  <si>
     <t>Жаштардын баштапкы кесиптик билим алгандардын үлүшү (калктын 15-17 жашын алганда)</t>
   </si>
   <si>
@@ -95,9 +90,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>4.3.1.1 Youth education by gender</t>
-  </si>
-  <si>
     <t>(пайыз менен)</t>
   </si>
   <si>
@@ -105,16 +97,25 @@
   </si>
   <si>
     <t>(in percent)</t>
+  </si>
+  <si>
+    <t>4.3.1.1 Доля молодежи от 15 до 24 лет, обучающихся в системе начального профессионального образования, среднего профессионального и высшего профессионального образования к численности населения соответствующего возраста</t>
+  </si>
+  <si>
+    <t>4.3.1.1 15–24 жаштагы баштапкы кесиптик, орто кесиптик жана жогорку кесиптик билим берүүдө окуп жаткан жаштардын үлүшү тиешелүү курактагы калктын жалпы санына карата</t>
+  </si>
+  <si>
+    <t>4.3.1.1 Proportion of youth aged 15–24 enrolled in initial vocational, secondary vocational and higher professional education among the population of the corresponding age group</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +161,38 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Cyr"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman CYR"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Cyr"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Helv"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="NTHarmonica"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -187,10 +220,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyFont="0" applyAlignment="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="38" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="40" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -198,9 +242,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -219,10 +260,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -231,24 +269,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="10">
+    <cellStyle name="Normal_PPI" xfId="2" xr:uid="{B1CA101C-8A6C-49E7-90DA-2FFE8330DCFA}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{99AD8307-6125-44B8-8873-9F16EDD8A7B6}"/>
+    <cellStyle name="Обычный 2 2" xfId="9" xr:uid="{412BB3FB-7F40-4B08-AFFD-4E2DC6A3A8CA}"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{771963BA-B1BB-4A6B-9880-CC2B1D398415}"/>
+    <cellStyle name="Обычный 4" xfId="8" xr:uid="{5531FBD3-4779-4CF5-A85C-6876201E5D62}"/>
+    <cellStyle name="полужирный" xfId="4" xr:uid="{A362B1FB-BB3C-4EB7-BC4C-9D96C024A6F5}"/>
+    <cellStyle name="Стиль 1" xfId="5" xr:uid="{435C4092-2D6C-4E4B-B948-444195984884}"/>
+    <cellStyle name="Тысячи [0]_Dannee" xfId="6" xr:uid="{6F86942C-978A-45BB-814C-5100D1758D25}"/>
+    <cellStyle name="Тысячи_Dannee" xfId="7" xr:uid="{07F19280-D227-4A3D-AD89-46D77070F4F6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -525,159 +568,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="35.5703125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="35.5703125" style="7" customWidth="1"/>
+    <col min="2" max="3" width="35.5703125" style="6" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="87.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.25" customHeight="1">
+      <c r="A2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="15"/>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2010</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2013</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2014</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2015</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2016</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2017</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2018</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2019</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2020</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2021</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2022</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2023</v>
+      </c>
+      <c r="P4" s="16">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" ht="37.5" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="F5" s="7">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G5" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="H5" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="I5" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="J5" s="7">
+        <v>10.1</v>
+      </c>
+      <c r="K5" s="9">
+        <v>10</v>
+      </c>
+      <c r="L5" s="9">
+        <v>10</v>
+      </c>
+      <c r="M5" s="9">
+        <v>10.8</v>
+      </c>
+      <c r="N5" s="9">
+        <v>9.224468514531754</v>
+      </c>
+      <c r="O5" s="9">
+        <v>7.9591147916539313</v>
+      </c>
+      <c r="P5" s="9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="6">
-        <v>2010</v>
-      </c>
-      <c r="E4" s="6">
-        <v>2013</v>
-      </c>
-      <c r="F4" s="6">
-        <v>2014</v>
-      </c>
-      <c r="G4" s="6">
-        <v>2015</v>
-      </c>
-      <c r="H4" s="6">
-        <v>2016</v>
-      </c>
-      <c r="I4" s="6">
-        <v>2017</v>
-      </c>
-      <c r="J4" s="6">
-        <v>2018</v>
-      </c>
-      <c r="K4" s="6">
-        <v>2019</v>
-      </c>
-      <c r="L4" s="6">
-        <v>2020</v>
-      </c>
-      <c r="M4" s="6">
-        <v>2021</v>
-      </c>
-      <c r="N4" s="6">
-        <v>2022</v>
-      </c>
-      <c r="O4" s="6">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" s="8" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8">
-        <v>9</v>
-      </c>
-      <c r="E5" s="8">
-        <v>9.4</v>
-      </c>
-      <c r="F5" s="8">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G5" s="8">
-        <v>9.5</v>
-      </c>
-      <c r="H5" s="8">
-        <v>10.4</v>
-      </c>
-      <c r="I5" s="8">
-        <v>10.9</v>
-      </c>
-      <c r="J5" s="8">
-        <v>10.1</v>
-      </c>
-      <c r="K5" s="10">
-        <v>10</v>
-      </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="10">
-        <v>10.8</v>
-      </c>
-      <c r="N5" s="10">
-        <v>9.224468514531754</v>
-      </c>
-      <c r="O5" s="10">
-        <v>7.9591147916539313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D6" s="2">
         <v>5.4</v>
@@ -700,31 +748,34 @@
       <c r="J6" s="2">
         <v>6.2</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>6.2</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>6.4</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>5.2</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="12">
         <v>4.6068543125097872</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="12">
         <v>4.1262815690193904</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="12">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="13.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
+      <c r="C7" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>12.5</v>
@@ -747,78 +798,84 @@
       <c r="J7" s="2">
         <v>13.9</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>13.7</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>13.5</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>16.2</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="12">
         <v>13.543910285971602</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="12">
         <v>11.553674062171684</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" s="8" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="P7" s="12">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="C8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7">
         <v>13.6</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>20.3</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>21.8</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>21.1</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>22</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>22.8</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>23.1</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="7">
         <v>23.1</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="7">
         <v>24.3</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="7">
         <v>24.2</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <v>24.703327617190443</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="9">
         <v>26.7840134279745</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="9">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>15</v>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D9" s="2">
         <v>16</v>
@@ -841,31 +898,34 @@
       <c r="J9" s="2">
         <v>26.4</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>26.5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>27.8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>27.6</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="12">
         <v>28.608474183838851</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="12">
         <v>31.703252552185106</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="12">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>18</v>
+      <c r="C10" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>11.2</v>
@@ -897,69 +957,75 @@
       <c r="M10" s="2">
         <v>20.9</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="12">
         <v>20.904451081350146</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="12">
         <v>22.127282549972989</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" s="8" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="P10" s="12">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" ht="37.5" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="E11" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="F11" s="7">
+        <v>23.8</v>
+      </c>
+      <c r="G11" s="7">
+        <v>22.6</v>
+      </c>
+      <c r="H11" s="7">
+        <v>20.2</v>
+      </c>
+      <c r="I11" s="7">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="J11" s="7">
+        <v>19.8</v>
+      </c>
+      <c r="K11" s="7">
+        <v>22.1</v>
+      </c>
+      <c r="L11" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="M11" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="N11" s="9">
+        <v>26.720095429750884</v>
+      </c>
+      <c r="O11" s="9">
+        <v>25.785751793343863</v>
+      </c>
+      <c r="P11" s="9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="8">
-        <v>24.3</v>
-      </c>
-      <c r="E11" s="8">
-        <v>24.3</v>
-      </c>
-      <c r="F11" s="8">
-        <v>23.8</v>
-      </c>
-      <c r="G11" s="8">
-        <v>22.6</v>
-      </c>
-      <c r="H11" s="8">
-        <v>20.2</v>
-      </c>
-      <c r="I11" s="8">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="J11" s="8">
-        <v>19.8</v>
-      </c>
-      <c r="K11" s="8">
-        <v>22.1</v>
-      </c>
-      <c r="L11" s="8">
-        <v>26.7</v>
-      </c>
-      <c r="M11" s="8">
-        <v>28.5</v>
-      </c>
-      <c r="N11" s="16">
-        <v>26.720095429750884</v>
-      </c>
-      <c r="O11" s="16">
-        <v>25.785751793343863</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="D12" s="2">
         <v>26.3</v>
@@ -991,58 +1057,64 @@
       <c r="M12" s="2">
         <v>29.7</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="12">
         <v>27.704327204727914</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="12">
         <v>27.265979822798002</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="P12" s="12">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15" customHeight="1" thickBot="1">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="3">
         <v>22.4</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>21.8</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>21.2</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>20.6</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="3">
         <v>18.3</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="3">
         <v>17.399999999999999</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>18.3</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="3">
         <v>20.8</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="3">
         <v>25</v>
       </c>
-      <c r="M13" s="4">
+      <c r="M13" s="3">
         <v>27.5</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="13">
         <v>25.731792255708452</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="13">
         <v>24.322552749117975</v>
+      </c>
+      <c r="P13" s="13">
+        <v>23.4</v>
       </c>
     </row>
   </sheetData>
